--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapAca.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapAca.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EF2677-CC50-47C6-9872-88382778C91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BFFFD7-C4C7-4B82-A262-76D73E48AAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88EE0680-D2AF-4D5B-8956-45525AF8EC55}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88EE0680-D2AF-4D5B-8956-45525AF8EC55}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>BÁO CÁO TIẾN ĐỘ HỌC TẬP (Academic)</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Trung bình tiến độ học tập thực tế</t>
   </si>
   <si>
+    <t>30/217</t>
+  </si>
+  <si>
     <t>Họ và tên</t>
   </si>
   <si>
@@ -72,38 +75,44 @@
     <t>A1: {0}</t>
   </si>
   <si>
+    <t>{0}</t>
+  </si>
+  <si>
+    <t>A2: {0}</t>
+  </si>
+  <si>
+    <t>B1: {0}</t>
+  </si>
+  <si>
+    <t>B1+: {0}</t>
+  </si>
+  <si>
+    <t>B2: {0}</t>
+  </si>
+  <si>
+    <t>C1: {0}</t>
+  </si>
+  <si>
+    <t>Ngày: {0}</t>
+  </si>
+  <si>
+    <t>Khóa học: {0}</t>
+  </si>
+  <si>
+    <t>Lớp: {0}</t>
+  </si>
+  <si>
+    <t>Khối: {0}</t>
+  </si>
+  <si>
     <t>Trạng thái: {0}</t>
-  </si>
-  <si>
-    <t>Khối: {0}</t>
-  </si>
-  <si>
-    <t>Lớp: {0}</t>
-  </si>
-  <si>
-    <t>Ngày: {0}</t>
-  </si>
-  <si>
-    <t>C1: {0}</t>
-  </si>
-  <si>
-    <t>B2: {0}</t>
-  </si>
-  <si>
-    <t>B1+: {0}</t>
-  </si>
-  <si>
-    <t>A2: {0}</t>
-  </si>
-  <si>
-    <t>B1: {0}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,22 +131,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -264,34 +257,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -622,8 +604,8 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="21.125" customWidth="1"/>
     <col min="4" max="4" width="19.75" customWidth="1"/>
     <col min="5" max="5" width="24.375" customWidth="1"/>
@@ -631,133 +613,141 @@
     <col min="7" max="7" width="25.375" customWidth="1"/>
     <col min="8" max="8" width="21.25" customWidth="1"/>
     <col min="9" max="9" width="31.75" customWidth="1"/>
-    <col min="10" max="10" width="24.875" customWidth="1"/>
+    <col min="10" max="10" width="25.25" customWidth="1"/>
     <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="10" t="s">
-        <v>18</v>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="3"/>
+      <c r="F2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="6">
+        <v>120</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="G6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="I6" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapAca.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapAca.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BFFFD7-C4C7-4B82-A262-76D73E48AAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B7A7E0-2271-41DE-B4A8-7EF224B6C277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88EE0680-D2AF-4D5B-8956-45525AF8EC55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>BÁO CÁO TIẾN ĐỘ HỌC TẬP (Academic)</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Trạng thái: {0}</t>
+  </si>
+  <si>
+    <t>UserName</t>
   </si>
 </sst>
 </file>
@@ -601,24 +604,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F0142A-F723-4522-A490-1E86EDDC20A7}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="21.125" customWidth="1"/>
-    <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="6" width="26.75" customWidth="1"/>
-    <col min="7" max="7" width="25.375" customWidth="1"/>
-    <col min="8" max="8" width="21.25" customWidth="1"/>
-    <col min="9" max="9" width="31.75" customWidth="1"/>
-    <col min="10" max="10" width="25.25" customWidth="1"/>
-    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="21.125" customWidth="1"/>
+    <col min="5" max="5" width="19.75" customWidth="1"/>
+    <col min="6" max="6" width="24.375" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
+    <col min="8" max="8" width="25.375" customWidth="1"/>
+    <col min="9" max="9" width="21.25" customWidth="1"/>
+    <col min="10" max="10" width="31.75" customWidth="1"/>
+    <col min="11" max="11" width="25.25" customWidth="1"/>
+    <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -630,132 +633,140 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="8"/>
+      <c r="K1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9"/>
+      <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="6">
+      <c r="E3" s="10"/>
+      <c r="F3" s="6">
         <v>120</v>
       </c>
-      <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapAca.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapAca.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B7A7E0-2271-41DE-B4A8-7EF224B6C277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F54B902-C9B6-4549-B029-EFA6A1EAE329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88EE0680-D2AF-4D5B-8956-45525AF8EC55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>BÁO CÁO TIẾN ĐỘ HỌC TẬP (Academic)</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Trung bình tiến độ học tập thực tế</t>
   </si>
   <si>
-    <t>30/217</t>
-  </si>
-  <si>
     <t>Họ và tên</t>
   </si>
   <si>
@@ -109,6 +106,12 @@
   </si>
   <si>
     <t>UserName</t>
+  </si>
+  <si>
+    <t>0/217</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -125,27 +128,26 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
@@ -260,35 +262,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,160 +608,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F0142A-F723-4522-A490-1E86EDDC20A7}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="21.125" customWidth="1"/>
-    <col min="5" max="5" width="19.75" customWidth="1"/>
-    <col min="6" max="6" width="24.375" customWidth="1"/>
-    <col min="7" max="7" width="26.75" customWidth="1"/>
-    <col min="8" max="8" width="25.375" customWidth="1"/>
-    <col min="9" max="9" width="21.25" customWidth="1"/>
-    <col min="10" max="10" width="31.75" customWidth="1"/>
-    <col min="11" max="11" width="25.25" customWidth="1"/>
-    <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15" style="7" customWidth="1"/>
+    <col min="4" max="4" width="21.125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="24.375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="26.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="25.375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="21.25" style="7" customWidth="1"/>
+    <col min="10" max="10" width="31.75" style="7" customWidth="1"/>
+    <col min="11" max="11" width="25.25" style="7" customWidth="1"/>
+    <col min="12" max="12" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="4" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="6">
-        <v>120</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="11" t="s">
         <v>13</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
